--- a/config/lines/华迪热熔胶复合机.xlsx
+++ b/config/lines/华迪热熔胶复合机.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="11760"/>
+    <workbookView windowWidth="28800" windowHeight="11775" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="配置" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="204">
   <si>
     <t>配置项</t>
   </si>
@@ -156,102 +156,102 @@
     <t>使用模拟数据</t>
   </si>
   <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>UseSimulator</t>
+  </si>
+  <si>
+    <t>MQTT_Broker</t>
+  </si>
+  <si>
+    <t>192.168.16.18</t>
+  </si>
+  <si>
+    <t>MqttHost</t>
+  </si>
+  <si>
+    <t>MQTT端口</t>
+  </si>
+  <si>
+    <t>1888</t>
+  </si>
+  <si>
+    <t>MqttPort</t>
+  </si>
+  <si>
+    <t>MQTT_ClientId</t>
+  </si>
+  <si>
+    <t>HDRRJFHJ</t>
+  </si>
+  <si>
+    <t>MqttClientId</t>
+  </si>
+  <si>
+    <t>MQTT_用户名</t>
+  </si>
+  <si>
+    <t>hg_iot</t>
+  </si>
+  <si>
+    <t>MqttUsername</t>
+  </si>
+  <si>
+    <t>MQTT_密码</t>
+  </si>
+  <si>
+    <t>Hg@Iot2026</t>
+  </si>
+  <si>
+    <t>MqttPassword</t>
+  </si>
+  <si>
+    <t>MQTT_TLS</t>
+  </si>
+  <si>
+    <t>MqttUseTls</t>
+  </si>
+  <si>
+    <t>MQTT_QoS</t>
+  </si>
+  <si>
+    <t>MqttQos</t>
+  </si>
+  <si>
+    <t>MQTT发布主题</t>
+  </si>
+  <si>
+    <t>/RRJFHJ/HDRRJFHJ/properties/report</t>
+  </si>
+  <si>
+    <t>MqttTopic</t>
+  </si>
+  <si>
+    <t>订阅主题</t>
+  </si>
+  <si>
+    <t>/RRJFHJ/XHRRJFHJ/properties/report;/RRJFHJ/HDRRJFHJ/properties/report;/RRJFHJ/SFHFJ/properties/report;/RRJFHJ/PBHFJ/properties/report;/RRJFHJ/CYHYFJ/properties/report</t>
+  </si>
+  <si>
+    <t>SubscribeTopics</t>
+  </si>
+  <si>
+    <t>运行模式</t>
+  </si>
+  <si>
+    <t>采集模式</t>
+  </si>
+  <si>
+    <t>OperationMode</t>
+  </si>
+  <si>
+    <t>开机自动启动</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
-    <t>UseSimulator</t>
-  </si>
-  <si>
-    <t>MQTT_Broker</t>
-  </si>
-  <si>
-    <t>192.168.16.18</t>
-  </si>
-  <si>
-    <t>MqttHost</t>
-  </si>
-  <si>
-    <t>MQTT端口</t>
-  </si>
-  <si>
-    <t>1888</t>
-  </si>
-  <si>
-    <t>MqttPort</t>
-  </si>
-  <si>
-    <t>MQTT_ClientId</t>
-  </si>
-  <si>
-    <t>HDRRJFHJ</t>
-  </si>
-  <si>
-    <t>MqttClientId</t>
-  </si>
-  <si>
-    <t>MQTT_用户名</t>
-  </si>
-  <si>
-    <t>hg_iot</t>
-  </si>
-  <si>
-    <t>MqttUsername</t>
-  </si>
-  <si>
-    <t>MQTT_密码</t>
-  </si>
-  <si>
-    <t>Hg@Iot2026</t>
-  </si>
-  <si>
-    <t>MqttPassword</t>
-  </si>
-  <si>
-    <t>MQTT_TLS</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>MqttUseTls</t>
-  </si>
-  <si>
-    <t>MQTT_QoS</t>
-  </si>
-  <si>
-    <t>MqttQos</t>
-  </si>
-  <si>
-    <t>MQTT发布主题</t>
-  </si>
-  <si>
-    <t>/RRJFHJ/HDRRJFHJ/properties/report</t>
-  </si>
-  <si>
-    <t>MqttTopic</t>
-  </si>
-  <si>
-    <t>订阅主题</t>
-  </si>
-  <si>
-    <t>/RRJFHJ/XHRRJFHJ/properties/report;/RRJFHJ/HDRRJFHJ/properties/report;/RRJFHJ/SFHFJ/properties/report;/RRJFHJ/PBHFJ/properties/report;/RRJFHJ/CYHYFJ/properties/report</t>
-  </si>
-  <si>
-    <t>SubscribeTopics</t>
-  </si>
-  <si>
-    <t>运行模式</t>
-  </si>
-  <si>
-    <t>采集模式</t>
-  </si>
-  <si>
-    <t>OperationMode</t>
-  </si>
-  <si>
-    <t>开机自动启动</t>
-  </si>
-  <si>
     <t>StartWithWindows</t>
   </si>
   <si>
@@ -412,12 +412,6 @@
   </si>
   <si>
     <t>胶水型号</t>
-  </si>
-  <si>
-    <t>cphh</t>
-  </si>
-  <si>
-    <t>产品货号</t>
   </si>
   <si>
     <t>mf</t>
@@ -1344,8 +1338,8 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{DE960A34-AA39-49EE-AB73-3EA1C850BCE2}"/>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{8E596314-5012-473B-BF93-CDF7CCE6EA9C}"/>
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{CBD626B9-ECF3-4039-9EA9-EBD289FC799C}"/>
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{EFCFC6B3-09DD-4E68-A611-C35961AD0090}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1795,7 +1789,7 @@
       <c r="A14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C14" t="s">
@@ -1862,62 +1856,62 @@
         <v>56</v>
       </c>
       <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
         <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="s">
         <v>61</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
         <v>64</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
         <v>67</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
         <v>70</v>
-      </c>
-      <c r="B25" t="s">
-        <v>39</v>
       </c>
       <c r="C25" t="s">
         <v>71</v>
@@ -1928,7 +1922,7 @@
         <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
         <v>73</v>
@@ -1939,7 +1933,7 @@
         <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
         <v>75</v>
@@ -2078,7 +2072,7 @@
         <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>98</v>
@@ -2094,7 +2088,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="10.5714285714286" customWidth="1"/>
@@ -2241,7 +2235,7 @@
       <c r="A18" t="s">
         <v>133</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2251,14 +2245,6 @@
       </c>
       <c r="B19" s="2" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2271,7 +2257,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.1428571428571" customWidth="1"/>
@@ -2288,43 +2274,43 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2332,22 +2318,22 @@
         <v>102</v>
       </c>
       <c r="B2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" t="s">
         <v>151</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" t="s">
         <v>152</v>
       </c>
-      <c r="D2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" t="s">
-        <v>154</v>
-      </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
         <v>84</v>
@@ -2362,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2373,22 +2359,22 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" t="s">
         <v>156</v>
       </c>
-      <c r="D3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E3" t="s">
-        <v>158</v>
-      </c>
       <c r="F3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
         <v>84</v>
@@ -2403,10 +2389,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2414,22 +2400,22 @@
         <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
         <v>84</v>
       </c>
       <c r="F4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H4" t="s">
         <v>84</v>
@@ -2444,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2455,22 +2441,22 @@
         <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H5" t="s">
         <v>84</v>
@@ -2485,10 +2471,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2496,22 +2482,22 @@
         <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H6" t="s">
         <v>84</v>
@@ -2526,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2537,22 +2523,22 @@
         <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
         <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H7" t="s">
         <v>84</v>
@@ -2567,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2578,22 +2564,22 @@
         <v>114</v>
       </c>
       <c r="B8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" t="s">
         <v>151</v>
       </c>
-      <c r="C8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D8" t="s">
-        <v>153</v>
-      </c>
       <c r="E8" t="s">
         <v>84</v>
       </c>
       <c r="F8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H8" t="s">
         <v>84</v>
@@ -2608,10 +2594,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M8" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2619,22 +2605,22 @@
         <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H9" t="s">
         <v>84</v>
@@ -2649,10 +2635,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M9" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2660,22 +2646,22 @@
         <v>118</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
         <v>84</v>
@@ -2690,10 +2676,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M10" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2701,22 +2687,22 @@
         <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H11" t="s">
         <v>84</v>
@@ -2731,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M11" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2742,22 +2728,22 @@
         <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C12" t="s">
         <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E12" t="s">
         <v>84</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
         <v>84</v>
@@ -2772,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M12" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2783,22 +2769,22 @@
         <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13" t="s">
         <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E13" t="s">
         <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H13" t="s">
         <v>84</v>
@@ -2813,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2824,22 +2810,22 @@
         <v>126</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
         <v>84</v>
       </c>
       <c r="D14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" t="s">
         <v>170</v>
       </c>
-      <c r="E14" t="s">
-        <v>84</v>
-      </c>
       <c r="F14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
         <v>84</v>
@@ -2854,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s">
         <v>39</v>
@@ -2865,22 +2851,22 @@
         <v>128</v>
       </c>
       <c r="B15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s">
         <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
         <v>84</v>
@@ -2895,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2906,22 +2892,22 @@
         <v>130</v>
       </c>
       <c r="B16" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
         <v>84</v>
@@ -2936,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="M16" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -2947,22 +2933,22 @@
         <v>132</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
         <v>84</v>
       </c>
       <c r="F17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>84</v>
@@ -2977,10 +2963,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M17" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -2988,22 +2974,22 @@
         <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E18" t="s">
         <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
         <v>84</v>
@@ -3018,33 +3004,30 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="M18" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
+      <c r="B19" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
         <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H19" t="s">
         <v>84</v>
@@ -3059,48 +3042,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D20" t="s">
-        <v>170</v>
-      </c>
-      <c r="E20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" t="s">
         <v>39</v>
-      </c>
-      <c r="H20" t="s">
-        <v>84</v>
-      </c>
-      <c r="I20" t="s">
-        <v>84</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20" t="s">
-        <v>171</v>
-      </c>
-      <c r="M20" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3124,96 +3069,96 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" t="s">
         <v>177</v>
-      </c>
-      <c r="C2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" t="s">
         <v>180</v>
-      </c>
-      <c r="C3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" t="s">
         <v>183</v>
-      </c>
-      <c r="C4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" t="s">
         <v>186</v>
-      </c>
-      <c r="C5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D5" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" t="s">
         <v>189</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>190</v>
-      </c>
-      <c r="C6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -3243,45 +3188,45 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
         <v>42</v>
@@ -3299,16 +3244,16 @@
         <v>54</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/config/lines/华迪热熔胶复合机.xlsx
+++ b/config/lines/华迪热熔胶复合机.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="配置" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="206">
   <si>
     <t>配置项</t>
   </si>
@@ -129,10 +129,16 @@
     <t>扫描周期毫秒</t>
   </si>
   <si>
+    <t>ScanIntervalMs</t>
+  </si>
+  <si>
+    <t>发布周期毫秒</t>
+  </si>
+  <si>
     <t>60000</t>
   </si>
   <si>
-    <t>ScanIntervalMs</t>
+    <t>PublishIntervalMs</t>
   </si>
   <si>
     <t>温度发布阈值</t>
@@ -661,7 +667,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -679,6 +685,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1136,155 +1148,156 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1338,8 +1351,8 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{CBD626B9-ECF3-4039-9EA9-EBD289FC799C}"/>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{EFCFC6B3-09DD-4E68-A611-C35961AD0090}"/>
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{E309C208-C7CB-4FED-A6FB-1E51CF1B796B}"/>
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{50770E64-2F28-4438-921E-DA5A4938A551}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1634,7 +1647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14.4285714285714" customWidth="1"/>
@@ -1756,107 +1769,107 @@
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>2000</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" t="s">
         <v>39</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
         <v>47</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
         <v>50</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
         <v>53</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
         <v>56</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>57</v>
@@ -1867,7 +1880,7 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
         <v>59</v>
@@ -1878,51 +1891,51 @@
         <v>60</v>
       </c>
       <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
         <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
         <v>63</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>64</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" t="s">
         <v>66</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
         <v>69</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" t="s">
         <v>72</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
       </c>
       <c r="C26" t="s">
         <v>73</v>
@@ -1933,7 +1946,7 @@
         <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
         <v>75</v>
@@ -1943,11 +1956,22 @@
       <c r="A28" t="s">
         <v>76</v>
       </c>
-      <c r="B28">
-        <v>1</v>
+      <c r="B28" t="s">
+        <v>72</v>
       </c>
       <c r="C28" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1981,101 +2005,101 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2097,154 +2121,154 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2274,72 +2298,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -2348,39 +2372,39 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" t="s">
         <v>154</v>
       </c>
-      <c r="D3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" t="s">
-        <v>152</v>
-      </c>
       <c r="G3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -2389,39 +2413,39 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -2430,39 +2454,39 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2471,39 +2495,39 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -2512,39 +2536,39 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -2553,39 +2577,39 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -2594,39 +2618,39 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2635,39 +2659,39 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2676,39 +2700,39 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2717,39 +2741,39 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2758,39 +2782,39 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2799,39 +2823,39 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2840,39 +2864,39 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2881,39 +2905,39 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2922,39 +2946,39 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2963,39 +2987,39 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -3004,36 +3028,36 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -3042,10 +3066,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3069,96 +3093,96 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3188,72 +3212,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>1888</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
